--- a/data/trans_orig/P57C2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57C2_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se ha sentido bien consigo mismo/a en 2023</t>
+          <t>Población según si se ha sentido bien consigo mismo/a en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2311</t>
+          <t>2218</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21392</t>
+          <t>21032</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22146</t>
+          <t>22372</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15579</t>
+          <t>14716</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16453</t>
+          <t>16435</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5964</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30838</t>
+          <t>30193</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16003</t>
+          <t>15440</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42754</t>
+          <t>41648</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25345</t>
+          <t>26071</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>57309</t>
+          <t>59407</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>142014</t>
+          <t>141550</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>212812</t>
+          <t>212804</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>93939</t>
+          <t>94643</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>137858</t>
+          <t>139893</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>249428</t>
+          <t>252714</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>335893</t>
+          <t>334380</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>46,89%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>174201</t>
+          <t>172969</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>242825</t>
+          <t>242760</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>135106</t>
+          <t>132962</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>182379</t>
+          <t>180808</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>321405</t>
+          <t>324049</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>407264</t>
+          <t>407435</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,13%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>163</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>9674</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>898</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9994</t>
+          <t>10113</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13808</t>
+          <t>14900</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23265</t>
+          <t>22671</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21931</t>
+          <t>21800</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12181</t>
+          <t>12204</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35822</t>
+          <t>35928</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19223</t>
+          <t>18716</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48425</t>
+          <t>48483</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>8242</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27013</t>
+          <t>27272</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30514</t>
+          <t>30930</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>66966</t>
+          <t>66177</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>144930</t>
+          <t>139855</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>196262</t>
+          <t>190923</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>127230</t>
+          <t>128273</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>243338</t>
+          <t>241529</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>280322</t>
+          <t>278258</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>417598</t>
+          <t>416745</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,57%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>185783</t>
+          <t>189278</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>240076</t>
+          <t>239555</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>231207</t>
+          <t>232758</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>369527</t>
+          <t>361265</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>437343</t>
+          <t>441246</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>610192</t>
+          <t>601270</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>64,3%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19054</t>
+          <t>18768</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>710</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8827</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23173</t>
+          <t>22506</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18389</t>
+          <t>17501</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11605</t>
+          <t>11594</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24874</t>
+          <t>24541</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19389</t>
+          <t>20098</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37592</t>
+          <t>39126</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17285</t>
+          <t>17493</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36473</t>
+          <t>36754</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26972</t>
+          <t>26391</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46645</t>
+          <t>45250</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>48537</t>
+          <t>48980</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74501</t>
+          <t>76035</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>203182</t>
+          <t>205566</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>250425</t>
+          <t>253087</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>240823</t>
+          <t>242946</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>278462</t>
+          <t>281290</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>458223</t>
+          <t>457607</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>515043</t>
+          <t>519943</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>48,2%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>240715</t>
+          <t>237051</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>288533</t>
+          <t>285666</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>208450</t>
+          <t>207419</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>245682</t>
+          <t>245155</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>457775</t>
+          <t>459847</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>520242</t>
+          <t>521290</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,32%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>4854</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27102</t>
+          <t>27156</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13651</t>
+          <t>14163</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11813</t>
+          <t>13327</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34551</t>
+          <t>34511</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40044</t>
+          <t>39715</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>16749</t>
+          <t>16973</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>32423</t>
+          <t>32400</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>28726</t>
+          <t>27418</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>64050</t>
+          <t>65318</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20206</t>
+          <t>18782</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>68997</t>
+          <t>69940</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>52503</t>
+          <t>53181</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>78438</t>
+          <t>80174</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>65602</t>
+          <t>67549</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>141003</t>
+          <t>140317</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>119030</t>
+          <t>131444</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>425300</t>
+          <t>424419</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>337280</t>
+          <t>335566</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>416880</t>
+          <t>418964</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>383417</t>
+          <t>404962</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>796398</t>
+          <t>803527</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>50,27%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>344783</t>
+          <t>345444</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>727467</t>
+          <t>717408</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>213396</t>
+          <t>214482</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>273264</t>
+          <t>274506</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>588135</t>
+          <t>582725</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1106738</t>
+          <t>1091318</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>68,27%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12871</t>
+          <t>13271</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6662</t>
+          <t>6791</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16826</t>
+          <t>17100</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11531</t>
+          <t>11109</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>26545</t>
+          <t>25329</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16184</t>
+          <t>15493</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>35234</t>
+          <t>34359</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17836</t>
+          <t>18078</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32509</t>
+          <t>32635</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>36603</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>60070</t>
+          <t>59166</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>56656</t>
+          <t>55161</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>86616</t>
+          <t>85393</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>75372</t>
+          <t>76238</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>100579</t>
+          <t>101243</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>136817</t>
+          <t>136785</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>176517</t>
+          <t>178150</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,11%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>270348</t>
+          <t>268765</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>314772</t>
+          <t>314690</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>263403</t>
+          <t>262535</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>297983</t>
+          <t>296956</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>543384</t>
+          <t>542782</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>600642</t>
+          <t>600321</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,3%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>148107</t>
+          <t>147067</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>186373</t>
+          <t>189632</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>127211</t>
+          <t>126815</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>157285</t>
+          <t>158300</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>286860</t>
+          <t>287701</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>338901</t>
+          <t>339450</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,7%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7958</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9566</t>
+          <t>9507</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>14275</t>
+          <t>14621</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6882</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>17056</t>
+          <t>17015</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t>9466</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>36884</t>
+          <t>36690</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16066</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>45551</t>
+          <t>45788</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>37548</t>
+          <t>39256</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>58588</t>
+          <t>58904</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>22551</t>
+          <t>23428</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>94099</t>
+          <t>94400</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>56163</t>
+          <t>55377</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>143228</t>
+          <t>142247</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>176182</t>
+          <t>175702</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>206650</t>
+          <t>206756</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>303141</t>
+          <t>301338</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>525137</t>
+          <t>525973</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>496227</t>
+          <t>495134</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>800818</t>
+          <t>782526</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>80,28%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>98757</t>
+          <t>99242</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>127806</t>
+          <t>126724</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>46820</t>
+          <t>45569</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>174382</t>
+          <t>174797</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>105130</t>
+          <t>115844</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>289816</t>
+          <t>290915</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>474</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>12088</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>14742</t>
+          <t>14409</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>9585</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>20696</t>
+          <t>21022</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>29466</t>
+          <t>29370</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>45825</t>
+          <t>45828</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>41944</t>
+          <t>42553</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>61989</t>
+          <t>63496</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>35792</t>
+          <t>34924</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>54664</t>
+          <t>54454</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>84359</t>
+          <t>85566</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>108390</t>
+          <t>108862</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,47 +5098,47 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
+          <t>20,31%</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>25,84%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>140924</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>125822</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>156050</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
           <t>20,03%</t>
         </is>
       </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>25,73%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>140924</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>126149</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>156206</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>20,03%</t>
-        </is>
-      </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>130140</t>
+          <t>128790</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>155408</t>
+          <t>156552</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>188054</t>
+          <t>189236</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>218059</t>
+          <t>218894</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>328521</t>
+          <t>325065</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>366159</t>
+          <t>364566</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>51,83%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>66326</t>
+          <t>66502</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>89243</t>
+          <t>90798</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>66337</t>
+          <t>66385</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>88918</t>
+          <t>88359</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>138215</t>
+          <t>139199</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>172290</t>
+          <t>171640</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>26604</t>
+          <t>27127</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>54883</t>
+          <t>55726</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>33102</t>
+          <t>34734</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>61712</t>
+          <t>62830</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>66397</t>
+          <t>68869</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>106374</t>
+          <t>107934</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>72639</t>
+          <t>70990</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>116190</t>
+          <t>113087</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>117397</t>
+          <t>117838</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>168718</t>
+          <t>169300</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>199827</t>
+          <t>199289</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>266420</t>
+          <t>268386</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>216855</t>
+          <t>218882</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>316633</t>
+          <t>317770</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>316667</t>
+          <t>312078</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>427922</t>
+          <t>427172</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>574294</t>
+          <t>574616</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>723130</t>
+          <t>724636</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1155429</t>
+          <t>1135032</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>1638418</t>
+          <t>1636233</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>1693005</t>
+          <t>1696913</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2132488</t>
+          <t>2165482</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>3023131</t>
+          <t>3023394</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3635967</t>
+          <t>3656725</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,44%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1380322</t>
+          <t>1379554</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1975948</t>
+          <t>2002004</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1044372</t>
+          <t>1055393</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1370878</t>
+          <t>1382655</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>2543893</t>
+          <t>2528757</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3260406</t>
+          <t>3237245</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,54%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57C2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57C2_2023-Edad-trans_orig.xlsx
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21032</t>
+          <t>25018</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2297</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22372</t>
+          <t>26577</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>9865</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2579</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14716</t>
+          <t>21676</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>9865</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16435</t>
+          <t>21627</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>18396</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>7878</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30193</t>
+          <t>36299</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26091</t>
+          <t>30292</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15440</t>
+          <t>18953</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41648</t>
+          <t>47437</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>39588</t>
+          <t>48688</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26071</t>
+          <t>31316</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59407</t>
+          <t>71353</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>176970</t>
+          <t>159844</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>141550</t>
+          <t>130140</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>212804</t>
+          <t>192866</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>115818</t>
+          <t>135840</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>94643</t>
+          <t>113102</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>139893</t>
+          <t>162728</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>292788</t>
+          <t>295684</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>252714</t>
+          <t>254454</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>334380</t>
+          <t>334018</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>43,36%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>209519</t>
+          <t>229553</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>172969</t>
+          <t>195834</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>242760</t>
+          <t>258019</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>156279</t>
+          <t>176791</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>132962</t>
+          <t>152206</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>180808</t>
+          <t>204267</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>365798</t>
+          <t>406343</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>324049</t>
+          <t>363339</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>407435</t>
+          <t>448165</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>58,18%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9674</t>
+          <t>11497</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>964</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10113</t>
+          <t>9256</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6454</t>
+          <t>7720</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14900</t>
+          <t>14820</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22671</t>
+          <t>20496</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12232</t>
+          <t>13478</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>7208</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21800</t>
+          <t>22732</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>22228</t>
+          <t>22805</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12204</t>
+          <t>13663</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35928</t>
+          <t>36033</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30175</t>
+          <t>35529</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18716</t>
+          <t>23113</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48483</t>
+          <t>52896</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16098</t>
+          <t>23384</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8242</t>
+          <t>13802</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27272</t>
+          <t>35772</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>46273</t>
+          <t>58913</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30930</t>
+          <t>42954</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>66177</t>
+          <t>79824</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>168077</t>
+          <t>184503</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>139855</t>
+          <t>156961</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>190923</t>
+          <t>211275</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>202702</t>
+          <t>224825</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>128273</t>
+          <t>202374</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>241529</t>
+          <t>248479</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>370779</t>
+          <t>409327</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>278258</t>
+          <t>373834</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>416745</t>
+          <t>445244</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>45,53%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>212816</t>
+          <t>243769</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>189278</t>
+          <t>217953</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>239555</t>
+          <t>274397</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>276502</t>
+          <t>235439</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>232758</t>
+          <t>213532</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>361265</t>
+          <t>258068</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>489318</t>
+          <t>479208</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>441246</t>
+          <t>445500</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>601270</t>
+          <t>517818</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>52,95%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10015</t>
+          <t>10695</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18768</t>
+          <t>23834</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>933</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7486</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>13045</t>
+          <t>13968</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6913</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22506</t>
+          <t>24650</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10454</t>
+          <t>12581</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>6686</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17501</t>
+          <t>20628</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17203</t>
+          <t>20450</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11594</t>
+          <t>13951</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24541</t>
+          <t>29965</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>27657</t>
+          <t>33031</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20098</t>
+          <t>23244</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39126</t>
+          <t>43884</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25961</t>
+          <t>31940</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17493</t>
+          <t>22415</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36754</t>
+          <t>46712</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>34564</t>
+          <t>40396</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26391</t>
+          <t>29814</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45250</t>
+          <t>51352</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>60526</t>
+          <t>72336</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>48980</t>
+          <t>58433</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>76035</t>
+          <t>89609</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>227539</t>
+          <t>259934</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>205566</t>
+          <t>232075</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>253087</t>
+          <t>286369</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>259986</t>
+          <t>295608</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>242946</t>
+          <t>276061</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>281290</t>
+          <t>317447</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>487525</t>
+          <t>555542</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>457607</t>
+          <t>522443</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>519943</t>
+          <t>586735</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>47,2%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>262369</t>
+          <t>305688</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>237051</t>
+          <t>278598</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>285666</t>
+          <t>333589</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>227685</t>
+          <t>262412</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>207419</t>
+          <t>242566</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>245155</t>
+          <t>280360</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>490054</t>
+          <t>568100</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>459847</t>
+          <t>536345</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>521290</t>
+          <t>601239</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,37%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>14727</t>
+          <t>15543</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>8502</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27156</t>
+          <t>27217</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,67 +2806,67 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7963</t>
+          <t>8914</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14163</t>
+          <t>14326</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>24457</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>16038</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>37658</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>1,12%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>22690</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>13327</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>34511</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>24134</t>
+          <t>25582</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>16180</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>39715</t>
+          <t>36550</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>23668</t>
+          <t>26443</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>16973</t>
+          <t>18437</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>32400</t>
+          <t>34820</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>47801</t>
+          <t>52025</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>27418</t>
+          <t>40886</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>65318</t>
+          <t>65718</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>45096</t>
+          <t>50060</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18782</t>
+          <t>35825</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>69940</t>
+          <t>64500</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>65863</t>
+          <t>73304</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>53181</t>
+          <t>61366</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>80174</t>
+          <t>87024</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>110959</t>
+          <t>123363</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>67549</t>
+          <t>103080</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>140317</t>
+          <t>143408</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>299022</t>
+          <t>325476</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>131444</t>
+          <t>297016</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>424419</t>
+          <t>353977</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>363424</t>
+          <t>356966</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>335566</t>
+          <t>335001</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>418964</t>
+          <t>377658</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>662445</t>
+          <t>682442</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>404962</t>
+          <t>648262</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>803527</t>
+          <t>715672</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>49,86%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>503808</t>
+          <t>283032</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>345444</t>
+          <t>255317</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>717408</t>
+          <t>311062</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>250857</t>
+          <t>270165</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>214482</t>
+          <t>250997</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>274506</t>
+          <t>293421</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>754666</t>
+          <t>553196</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>582725</t>
+          <t>521138</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1091318</t>
+          <t>589024</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>41,03%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>886787</t>
+          <t>699693</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>886787</t>
+          <t>699693</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>886787</t>
+          <t>699693</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>711775</t>
+          <t>735791</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>711775</t>
+          <t>735791</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>711775</t>
+          <t>735791</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1598562</t>
+          <t>1435484</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1598562</t>
+          <t>1435484</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1598562</t>
+          <t>1435484</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,67 +3453,67 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13271</t>
+          <t>14445</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>11901</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>7220</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>18058</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
           <t>1,19%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>10903</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>6791</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>17100</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>17551</t>
+          <t>19044</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>25329</t>
+          <t>27322</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>23226</t>
+          <t>25355</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15493</t>
+          <t>16208</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>34359</t>
+          <t>36181</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>24135</t>
+          <t>27394</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18078</t>
+          <t>19647</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32635</t>
+          <t>35902</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>47360</t>
+          <t>52749</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>36603</t>
+          <t>40631</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>59166</t>
+          <t>65901</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>69534</t>
+          <t>73229</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>55161</t>
+          <t>59125</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>85393</t>
+          <t>89151</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>87511</t>
+          <t>95982</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>76238</t>
+          <t>82836</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>101243</t>
+          <t>110121</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>157045</t>
+          <t>169211</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>136785</t>
+          <t>150490</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>178150</t>
+          <t>190041</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>292572</t>
+          <t>317828</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>268765</t>
+          <t>295005</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>314690</t>
+          <t>341950</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>280325</t>
+          <t>307982</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>262535</t>
+          <t>288321</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>296956</t>
+          <t>326805</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>572896</t>
+          <t>625810</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>542782</t>
+          <t>594925</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>600321</t>
+          <t>653636</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>53,81%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>168257</t>
+          <t>184804</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>147067</t>
+          <t>162190</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>189632</t>
+          <t>205733</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>142515</t>
+          <t>163037</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>126815</t>
+          <t>146049</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>158300</t>
+          <t>181513</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>310772</t>
+          <t>347841</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>287701</t>
+          <t>323233</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>339450</t>
+          <t>377046</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>545388</t>
+          <t>606296</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>545388</t>
+          <t>606296</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>545388</t>
+          <t>606296</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1105624</t>
+          <t>1214655</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1105624</t>
+          <t>1214655</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1105624</t>
+          <t>1214655</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7748</t>
+          <t>8787</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>9527</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>8628</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>14621</t>
+          <t>14881</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>10834</t>
+          <t>11484</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6751</t>
+          <t>6719</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>17015</t>
+          <t>17308</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>22226</t>
+          <t>24525</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>18463</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>36690</t>
+          <t>31750</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>33060</t>
+          <t>36009</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16688</t>
+          <t>27621</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>45788</t>
+          <t>45806</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>48082</t>
+          <t>51726</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>39256</t>
+          <t>40943</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>58904</t>
+          <t>62896</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>59231</t>
+          <t>61532</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>23428</t>
+          <t>51191</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>94400</t>
+          <t>73233</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>107314</t>
+          <t>113258</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>55377</t>
+          <t>97907</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>142247</t>
+          <t>129506</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>191629</t>
+          <t>213373</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>175702</t>
+          <t>196821</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>206756</t>
+          <t>230452</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>410220</t>
+          <t>222906</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>301338</t>
+          <t>207698</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>525973</t>
+          <t>237656</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>601849</t>
+          <t>436278</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>495134</t>
+          <t>413346</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>782526</t>
+          <t>460987</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>54,59%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>112474</t>
+          <t>125196</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>99242</t>
+          <t>109077</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>126724</t>
+          <t>141393</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>111393</t>
+          <t>124382</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>45569</t>
+          <t>112623</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>174797</t>
+          <t>139096</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>223867</t>
+          <t>249578</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>115844</t>
+          <t>227992</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>290915</t>
+          <t>269436</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>31,91%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>366892</t>
+          <t>405859</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>366892</t>
+          <t>405859</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>366892</t>
+          <t>405859</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>607826</t>
+          <t>438554</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>607826</t>
+          <t>438554</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>607826</t>
+          <t>438554</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>974718</t>
+          <t>844413</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>974718</t>
+          <t>844413</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>974718</t>
+          <t>844413</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,17 +4817,17 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>475</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>7826</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4965</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>13855</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,22 +4887,22 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>9490</t>
+          <t>10347</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>6522</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>14409</t>
+          <t>15778</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>14715</t>
+          <t>16049</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>9585</t>
+          <t>10444</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>21022</t>
+          <t>23168</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>37068</t>
+          <t>42037</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>29370</t>
+          <t>33316</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>45828</t>
+          <t>52448</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>51783</t>
+          <t>58086</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>42553</t>
+          <t>47833</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>63496</t>
+          <t>70797</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>44519</t>
+          <t>48926</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>34924</t>
+          <t>40620</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>54454</t>
+          <t>60762</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>96405</t>
+          <t>104521</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>85566</t>
+          <t>91992</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>108862</t>
+          <t>118437</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>140924</t>
+          <t>153447</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>125822</t>
+          <t>137283</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>156050</t>
+          <t>172038</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>142989</t>
+          <t>154110</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>128790</t>
+          <t>138821</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>156552</t>
+          <t>168713</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>203112</t>
+          <t>218639</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>189236</t>
+          <t>202549</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>218894</t>
+          <t>233690</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>346100</t>
+          <t>372749</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>325065</t>
+          <t>352602</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>364566</t>
+          <t>396287</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,51%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>78278</t>
+          <t>88622</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>66502</t>
+          <t>75564</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>90798</t>
+          <t>102132</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>76832</t>
+          <t>86055</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>66385</t>
+          <t>73448</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>88359</t>
+          <t>97953</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>155109</t>
+          <t>174678</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>139199</t>
+          <t>157767</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>171640</t>
+          <t>195949</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>25,47%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>282165</t>
+          <t>309527</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>282165</t>
+          <t>309527</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>282165</t>
+          <t>309527</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>421242</t>
+          <t>459781</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>421242</t>
+          <t>459781</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>421242</t>
+          <t>459781</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>703407</t>
+          <t>769307</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>703407</t>
+          <t>769307</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>703407</t>
+          <t>769307</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,102 +5499,102 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>39411</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>27127</t>
+          <t>30403</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>55726</t>
+          <t>58773</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>51507</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>38823</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>67059</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>94551</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>75345</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>116989</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
           <t>1,61%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>46285</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>34734</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>62830</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>85695</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>68869</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>107934</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -5612,102 +5612,102 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>93358</t>
+          <t>100378</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>70990</t>
+          <t>82025</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>113087</t>
+          <t>120209</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>164192</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>143807</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>186952</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>4,41%</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>5,02%</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>264570</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>237487</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>298730</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
           <t>3,27%</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>143707</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>117838</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>169300</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>3,93%</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>237065</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>199289</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>268386</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>276865</t>
+          <t>309805</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>218882</t>
+          <t>278281</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>317770</t>
+          <t>344022</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>385763</t>
+          <t>429411</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>312078</t>
+          <t>394201</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>427172</t>
+          <t>459904</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>662629</t>
+          <t>739216</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>574616</t>
+          <t>693846</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>724636</t>
+          <t>788008</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>1498798</t>
+          <t>1615067</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1135032</t>
+          <t>1550733</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>1636233</t>
+          <t>1684908</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>1835584</t>
+          <t>1762765</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>1696913</t>
+          <t>1707913</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2165482</t>
+          <t>1820765</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>3334382</t>
+          <t>3377832</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>3023394</t>
+          <t>3287379</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3656725</t>
+          <t>3460626</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>47,7%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>1547522</t>
+          <t>1460664</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1379554</t>
+          <t>1391715</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2002004</t>
+          <t>1529256</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>1242062</t>
+          <t>1318280</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1055393</t>
+          <t>1265172</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1382655</t>
+          <t>1370305</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>2789584</t>
+          <t>2778945</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>2528757</t>
+          <t>2698007</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3237245</t>
+          <t>2867238</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>39,52%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>3455954</t>
+          <t>3528958</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>3455954</t>
+          <t>3528958</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>3455954</t>
+          <t>3528958</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3653401</t>
+          <t>3726155</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>3653401</t>
+          <t>3726155</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3653401</t>
+          <t>3726155</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>7109355</t>
+          <t>7255114</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>7109355</t>
+          <t>7255114</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>7109355</t>
+          <t>7255114</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
